--- a/data/trans_camb/Q45B_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/Q45B_R-Edad-trans_camb.xlsx
@@ -631,17 +631,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,48</t>
+          <t>-0,64; 3,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,64</t>
+          <t>-2,81; 0,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 1,91</t>
+          <t>-6,75; 1,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 1,69</t>
+          <t>-2,9; 1,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,78; -1,88</t>
+          <t>-5,84; -1,85</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,3; 257,8</t>
+          <t>-22,26; 343,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-86,46; 61,38</t>
+          <t>-85,25; 84,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,14; 18,36</t>
+          <t>-47,21; 13,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-72,35; -28,54</t>
+          <t>-71,56; -29,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,11; 28,89</t>
+          <t>-34,61; 27,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,16; -27,3</t>
+          <t>-69,32; -29,77</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,84</t>
+          <t>-2,15; 1,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,65</t>
+          <t>-3,0; 0,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 4,05</t>
+          <t>-5,05; 3,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -6,21</t>
+          <t>-13,73; -6,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,22</t>
+          <t>-2,64; 2,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,33; -2,87</t>
+          <t>-6,99; -2,83</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,03; 71,47</t>
+          <t>-47,46; 76,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,53; 30,83</t>
+          <t>-63,17; 37,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 24,13</t>
+          <t>-25,14; 22,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-67,43; -36,99</t>
+          <t>-67,16; -37,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 23,51</t>
+          <t>-22,9; 23,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,26; -29,77</t>
+          <t>-60,5; -31,14</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,53</t>
+          <t>-0,72; 2,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; -0,34</t>
+          <t>-2,76; -0,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,59</t>
+          <t>-1,84; 3,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,63; -0,77</t>
+          <t>-5,68; -0,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,36</t>
+          <t>-0,93; 2,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -1,08</t>
+          <t>-3,87; -0,93</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,1; 182,13</t>
+          <t>-28,43; 179,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-93,05; -6,69</t>
+          <t>-92,12; -11,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-23,28; 64,2</t>
+          <t>-23,31; 64,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-67,33; -11,08</t>
+          <t>-66,95; -8,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 62,82</t>
+          <t>-17,73; 64,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,81; -26,9</t>
+          <t>-69,46; -23,59</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 3,59</t>
+          <t>-0,2; 3,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,46</t>
+          <t>-2,31; 0,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 2,75</t>
+          <t>-2,75; 2,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 0,59</t>
+          <t>-4,22; 0,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,56</t>
+          <t>-0,75; 2,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,08</t>
+          <t>-2,88; -0,03</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 737,63</t>
+          <t>-20,76; 619,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,28</t>
+          <t>-93,62; 146,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 77,23</t>
+          <t>-45,33; 68,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-66,64; 21,96</t>
+          <t>-66,79; 18,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 109,08</t>
+          <t>-21,13; 99,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,3; 4,7</t>
+          <t>-65,0; 4,28</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,82</t>
+          <t>-2,26; 0,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,7</t>
+          <t>-3,53; -0,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,7</t>
+          <t>-2,3; 1,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,39</t>
+          <t>-2,68; 1,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,77</t>
+          <t>-1,76; 0,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,03</t>
+          <t>-2,38; 0,01</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>-87,57; 193,36</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-73,5; 169,01</t>
+          <t>-72,84; 179,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-77,11; 172,21</t>
+          <t>-75,94; 152,18</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,32; 64,76</t>
+          <t>-66,38; 77,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-85,12; 13,62</t>
+          <t>-85,43; 10,09</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,72</t>
+          <t>-1,17; 1,44</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,02</t>
+          <t>-0,76; 2,02</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 3,32</t>
+          <t>-1,25; 3,45</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,96; -0,24</t>
+          <t>-3,29; -0,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,09</t>
+          <t>-0,95; 1,8</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,43</t>
+          <t>-1,51; 0,51</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-64,09; 487,74</t>
+          <t>-70,12; 438,43</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1507,12 +1507,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 327,42</t>
+          <t>-60,17; 261,4</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-84,56; 115,64</t>
+          <t>-84,74; 114,18</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1577,22 +1577,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,82</t>
+          <t>-0,05; 3,55</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,0</t>
+          <t>-2,52; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,51</t>
+          <t>0,27; 2,69</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,0</t>
+          <t>-1,24; 0,0</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-36,73; —</t>
+          <t>-59,33; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-50,1; —</t>
+          <t>-15,96; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,26</t>
+          <t>-0,26; 1,32</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,73; -0,51</t>
+          <t>-1,69; -0,5</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,89</t>
+          <t>-1,76; 0,93</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,34; -3,15</t>
+          <t>-5,45; -3,15</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,85</t>
+          <t>-0,77; 0,79</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,26; -1,96</t>
+          <t>-3,36; -2,01</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 70,85</t>
+          <t>-11,06; 79,75</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-69,95; -27,59</t>
+          <t>-69,2; -27,51</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 12,06</t>
+          <t>-20,42; 13,24</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-63,85; -44,43</t>
+          <t>-63,45; -43,78</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 18,75</t>
+          <t>-14,2; 16,85</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-61,9; -44,32</t>
+          <t>-62,24; -44,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Q45B_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/Q45B_R-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,48</t>
+          <t>-0,64; 3,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,7</t>
+          <t>-2,82; 0,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 1,43</t>
+          <t>-6,51; 1,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,24; -3,11</t>
+          <t>-10,44; -3,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,65</t>
+          <t>-2,87; 1,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,84; -1,85</t>
+          <t>-6,07; -1,94</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,26; 343,68</t>
+          <t>-27,99; 295,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,25; 84,35</t>
+          <t>-85,24; 75,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 13,77</t>
+          <t>-45,56; 18,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-71,56; -29,4</t>
+          <t>-72,17; -29,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 27,24</t>
+          <t>-35,34; 30,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,32; -29,77</t>
+          <t>-69,57; -27,4</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,99</t>
+          <t>-2,33; 1,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,91</t>
+          <t>-3,11; 0,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 3,62</t>
+          <t>-5,17; 3,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,73; -6,02</t>
+          <t>-13,89; -6,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 2,16</t>
+          <t>-2,51; 2,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; -2,83</t>
+          <t>-7,19; -2,89</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,46; 76,56</t>
+          <t>-47,43; 67,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-63,17; 37,94</t>
+          <t>-67,05; 32,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 22,87</t>
+          <t>-24,53; 22,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-67,16; -37,82</t>
+          <t>-66,19; -37,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 23,31</t>
+          <t>-21,66; 25,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,5; -31,14</t>
+          <t>-61,47; -30,79</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,63</t>
+          <t>-0,76; 2,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; -0,42</t>
+          <t>-2,85; -0,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 3,69</t>
+          <t>-2,12; 3,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,68; -0,75</t>
+          <t>-5,51; -0,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,42</t>
+          <t>-0,76; 2,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,87; -0,93</t>
+          <t>-3,97; -1,17</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,43; 179,72</t>
+          <t>-33,8; 172,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-92,12; -11,8</t>
+          <t>-93,58; -19,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 64,56</t>
+          <t>-26,3; 60,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-66,95; -8,41</t>
+          <t>-65,99; -9,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 64,77</t>
+          <t>-14,32; 67,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,46; -23,59</t>
+          <t>-71,14; -29,3</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 3,55</t>
+          <t>-0,14; 3,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,43</t>
+          <t>-2,1; 0,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,51</t>
+          <t>-2,52; 2,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,48</t>
+          <t>-4,35; 0,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,42</t>
+          <t>-0,81; 2,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,88; -0,03</t>
+          <t>-2,67; 0,08</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 619,29</t>
+          <t>-25,88; 631,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-93,62; 146,28</t>
+          <t>-100,0; 125,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,33; 68,16</t>
+          <t>-41,52; 77,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-66,79; 18,37</t>
+          <t>-68,39; 19,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 99,32</t>
+          <t>-21,22; 98,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,0; 4,28</t>
+          <t>-66,65; 4,31</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,97</t>
+          <t>-2,39; 0,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,53; -0,56</t>
+          <t>-3,47; -0,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,57</t>
+          <t>-2,31; 1,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,35</t>
+          <t>-2,73; 1,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,84</t>
+          <t>-1,75; 0,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,01</t>
+          <t>-2,33; 0,0</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-87,57; 193,36</t>
+          <t>-88,35; 190,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-72,84; 179,93</t>
+          <t>-69,59; 153,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-75,94; 152,18</t>
+          <t>-77,29; 112,88</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,38; 77,47</t>
+          <t>-66,97; 70,66</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-85,43; 10,09</t>
+          <t>-86,41; 8,46</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,44</t>
+          <t>-1,18; 1,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,02</t>
+          <t>-0,86; 2,07</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,45</t>
+          <t>-1,27; 3,52</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,29; -0,27</t>
+          <t>-3,44; -0,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,8</t>
+          <t>-0,72; 2,02</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,51</t>
+          <t>-1,42; 0,51</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-70,12; 438,43</t>
+          <t>-67,31; 488,68</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1507,12 +1507,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 261,4</t>
+          <t>-53,9; 360,87</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-84,74; 114,18</t>
+          <t>-88,75; 95,75</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1577,22 +1577,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 3,55</t>
+          <t>0,01; 3,56</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,0</t>
+          <t>-2,16; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,69</t>
+          <t>0,26; 2,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,0</t>
+          <t>-1,38; 0,0</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-59,33; —</t>
+          <t>-50,71; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,96; —</t>
+          <t>-40,1; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,32</t>
+          <t>-0,18; 1,25</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,69; -0,5</t>
+          <t>-1,67; -0,52</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,93</t>
+          <t>-1,63; 0,88</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,45; -3,15</t>
+          <t>-5,3; -3,3</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,79</t>
+          <t>-0,81; 0,77</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -2,01</t>
+          <t>-3,36; -2,06</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 79,75</t>
+          <t>-8,07; 74,54</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-69,2; -27,51</t>
+          <t>-69,15; -30,29</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-20,42; 13,24</t>
+          <t>-19,29; 12,49</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-63,45; -43,78</t>
+          <t>-62,81; -45,11</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 16,85</t>
+          <t>-14,77; 16,69</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-62,24; -44,25</t>
+          <t>-62,65; -45,22</t>
         </is>
       </c>
     </row>
